--- a/events/PonteDeLima_2022_MAR/PonteDeLima_2022_MAR_Results.xlsx
+++ b/events/PonteDeLima_2022_MAR/PonteDeLima_2022_MAR_Results.xlsx
@@ -2212,6 +2212,11 @@
           <t>01:51:10.810</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>126187</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5797,6 +5802,11 @@
           <t>00:14:42.830</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>65545</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6442,6 +6452,11 @@
           <t>00:13:41.540</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7152,6 +7167,11 @@
           <t>00:16:30.860</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>118969</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7279,6 +7299,11 @@
           <t>01:39:31.460</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>128721</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9546,6 +9571,11 @@
           <t>00:16:24.150</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11747,6 +11777,11 @@
           <t>00:13:17.480</t>
         </is>
       </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13117,6 +13152,11 @@
           <t>112891</t>
         </is>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>128306</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13179,6 +13219,11 @@
           <t>01:35:15.650</t>
         </is>
       </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>104760</t>
+        </is>
+      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>128717</t>
@@ -13606,6 +13651,11 @@
           <t>01:37:25.110</t>
         </is>
       </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>110845</t>
+        </is>
+      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>110846</t>
@@ -14871,6 +14921,11 @@
           <t>01:55:01.620</t>
         </is>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>98603</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15999,6 +16054,11 @@
           <t>01:33:53.250</t>
         </is>
       </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>128719</t>
+        </is>
+      </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>114632</t>
@@ -17294,6 +17354,11 @@
           <t>01:57:36.570</t>
         </is>
       </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>79270</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -18428,6 +18493,11 @@
           <t>02:03:08.460</t>
         </is>
       </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>118969</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -18935,6 +19005,11 @@
           <t>01:41:41.740</t>
         </is>
       </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>110840</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -18997,6 +19072,11 @@
           <t>01:41:54.540</t>
         </is>
       </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>112065</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -19260,6 +19340,11 @@
           <t>01:43:59.500</t>
         </is>
       </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>128713</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -19657,6 +19742,11 @@
           <t>01:47:43.340</t>
         </is>
       </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>112783</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -24674,6 +24764,11 @@
           <t>02:11:12.030</t>
         </is>
       </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -26076,6 +26171,11 @@
           <t>02:29:15.470</t>
         </is>
       </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>65545</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -26194,6 +26294,11 @@
       <c r="L388" t="n">
         <v>451</v>
       </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>126177</t>
+        </is>
+      </c>
       <c r="X388" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -26394,6 +26499,11 @@
           <t>01:34:33.690</t>
         </is>
       </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>116917</t>
+        </is>
+      </c>
       <c r="S391" t="inlineStr">
         <is>
           <t>116918</t>
@@ -26461,6 +26571,11 @@
           <t>01:34:40.360</t>
         </is>
       </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>128713</t>
+        </is>
+      </c>
       <c r="S392" t="inlineStr">
         <is>
           <t>128710</t>
@@ -26533,6 +26648,11 @@
           <t>112737</t>
         </is>
       </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>112783</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -26667,6 +26787,11 @@
           <t>01:37:17.130</t>
         </is>
       </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>112065</t>
+        </is>
+      </c>
       <c r="S395" t="inlineStr">
         <is>
           <t>112066</t>
@@ -26739,6 +26864,11 @@
           <t>122397</t>
         </is>
       </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>109339</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -27017,6 +27147,11 @@
           <t>01:39:41.600</t>
         </is>
       </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>128617</t>
+        </is>
+      </c>
       <c r="S400" t="inlineStr">
         <is>
           <t>128618</t>
@@ -27084,6 +27219,11 @@
           <t>01:40:05.370</t>
         </is>
       </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>113745</t>
+        </is>
+      </c>
       <c r="S401" t="inlineStr">
         <is>
           <t>113747</t>
@@ -27721,6 +27861,11 @@
           <t>111727</t>
         </is>
       </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>110840</t>
+        </is>
+      </c>
       <c r="X410" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -28274,6 +28419,16 @@
           <t>02:08:28.510</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -28977,6 +29132,11 @@
           <t>110847</t>
         </is>
       </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -29394,6 +29554,11 @@
           <t>02:05:23.540</t>
         </is>
       </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>98603</t>
+        </is>
+      </c>
       <c r="S434" t="inlineStr">
         <is>
           <t>76848</t>
@@ -29605,6 +29770,11 @@
           <t>02:06:42.640</t>
         </is>
       </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>128306</t>
+        </is>
+      </c>
       <c r="S437" t="inlineStr">
         <is>
           <t>42965</t>
@@ -29744,6 +29914,16 @@
           <t>02:10:35.070</t>
         </is>
       </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>91292</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -30088,6 +30268,11 @@
           <t>01:58:40.590</t>
         </is>
       </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S444" t="inlineStr">
         <is>
           <t>88713</t>
@@ -30376,6 +30561,11 @@
           <t>87418</t>
         </is>
       </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>87419</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -31014,6 +31204,11 @@
           <t>02:07:50.190</t>
         </is>
       </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>79270</t>
+        </is>
+      </c>
       <c r="S457" t="inlineStr">
         <is>
           <t>69239</t>
@@ -31285,6 +31480,11 @@
       </c>
       <c r="L461" t="n">
         <v>559</v>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>65545</t>
+        </is>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -31506,7 +31706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D312"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38373,6 +38573,578 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Annesofie</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>WINTHER</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>65545</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>CONCHA</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>GOMES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>COELHO</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>79270</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Nestor Damian</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>PINTA</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>87419</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>FERNANDEZ CASTANON</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>91292</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>98603</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>REGO GOMES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>104760</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Maja</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>HORVATH</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>109339</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Joshua</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>110840</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Bertram Sollann</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>SORENSEN</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>110845</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Sara Bressendorff</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>ANDERSEN</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>112065</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>112783</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>COETZER</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>113745</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Anton</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>HINGE</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>116917</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Baltazar Josue</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>ITRIA</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>118969</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>MOHAMED</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>126177</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Lajos</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>GYOKOS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>126187</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Mayu</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>ANDO</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>128306</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Matilda</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ENOCH</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>128617</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>BENTO</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>128713</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>VERGAUVEN</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>128719</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Zsombor</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>SZEGI</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>128721</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Dario</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/PonteDeLima_2022_MAR/PonteDeLima_2022_MAR_Results.xlsx
+++ b/events/PonteDeLima_2022_MAR/PonteDeLima_2022_MAR_Results.xlsx
@@ -4182,6 +4182,11 @@
           <t>00:15:35.970</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10375,6 +10380,11 @@
           <t>00:14:54.800</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -23444,6 +23454,11 @@
       <c r="P345" t="inlineStr">
         <is>
           <t>02:06:56.710</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>47779</t>
         </is>
       </c>
     </row>
@@ -31706,7 +31721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39145,6 +39160,28 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
